--- a/artfynd/A 31238-2022 artfynd.xlsx
+++ b/artfynd/A 31238-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>117441434</v>
       </c>
       <c r="B4" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>117565865</v>
       </c>
       <c r="B5" t="n">
-        <v>102874</v>
+        <v>102876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31238-2022 artfynd.xlsx
+++ b/artfynd/A 31238-2022 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>118762906</v>
       </c>
       <c r="B6" t="n">
-        <v>102885</v>
+        <v>102892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 31238-2022 artfynd.xlsx
+++ b/artfynd/A 31238-2022 artfynd.xlsx
@@ -675,57 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117430746</v>
+        <v>117430026</v>
       </c>
       <c r="B2" t="n">
-        <v>103511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220461</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågstugan 300m SSO, Srm</t>
+          <t>Sågstugan 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604576</v>
+        <v>604577</v>
       </c>
       <c r="R2" t="n">
-        <v>6553103</v>
+        <v>6553218</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117430026</v>
+        <v>117565865</v>
       </c>
       <c r="B3" t="n">
-        <v>102874</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,16 +822,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -839,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågstugan 200m SSO, Srm</t>
+          <t>Sågstugan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604577</v>
+        <v>604580</v>
       </c>
       <c r="R3" t="n">
-        <v>6553218</v>
+        <v>6553233</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,35 +885,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsmark hygge</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Karl Soler Kinnerbäck, Teresa Soler</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117441434</v>
+        <v>118762906</v>
       </c>
       <c r="B4" t="n">
-        <v>108705</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,16 +911,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>706</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,24 +928,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sågstugan 150m SO, Srm</t>
+          <t>Sågstugan, 150 m SO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604585</v>
+        <v>604588</v>
       </c>
       <c r="R4" t="n">
-        <v>6553284</v>
+        <v>6553252</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 ex, de flesta i blom</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,39 +993,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Kalhygge</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117565865</v>
+        <v>117441434</v>
       </c>
       <c r="B5" t="n">
-        <v>102876</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>706</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,23 +1046,19 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sågstugan, Srm</t>
+          <t>Sågstugan 150m SO, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604580</v>
+        <v>604585</v>
       </c>
       <c r="R5" t="n">
-        <v>6553233</v>
+        <v>6553284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,77 +1103,72 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Teresa Soler</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118762906</v>
+        <v>117430746</v>
       </c>
       <c r="B6" t="n">
-        <v>102897</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>706</v>
+        <v>220461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sågstugan, 150 m SO, Srm</t>
+          <t>Sågstugan 300m SSO, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604588</v>
+        <v>604576</v>
       </c>
       <c r="R6" t="n">
-        <v>6553252</v>
+        <v>6553103</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,17 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 ex, de flesta i blom</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,23 +1206,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalhygge</t>
+          <t>Skogsmark hygge</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 31238-2022 artfynd.xlsx
+++ b/artfynd/A 31238-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117565865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762906</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117441434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,8 +1252,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>